--- a/IPC_Grupo.xlsx
+++ b/IPC_Grupo.xlsx
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>0.416339534166917</v>
+        <v>0.4163395341669171</v>
       </c>
       <c r="C2" s="2">
-        <v>115.1522772893642</v>
+        <v>115.1522772893644</v>
       </c>
       <c r="D2" s="2">
         <v>0.416339534166917</v>
@@ -462,10 +462,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>0.02114957685449436</v>
+        <v>0.02114957685449437</v>
       </c>
       <c r="C3" s="2">
-        <v>119.5149351150946</v>
+        <v>119.5149351150945</v>
       </c>
       <c r="D3" s="2">
         <v>0.02114957685449436</v>
@@ -476,13 +476,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>0.06348000917680563</v>
+        <v>0.06348000917680566</v>
       </c>
       <c r="C4" s="2">
         <v>104.4278323948381</v>
       </c>
       <c r="D4" s="2">
-        <v>0.06348000917680563</v>
+        <v>0.06348000917680564</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -510,7 +510,7 @@
         <v>110.8521113458137</v>
       </c>
       <c r="D6" s="2">
-        <v>0.03095859502448804</v>
+        <v>0.03095859502448803</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -521,7 +521,7 @@
         <v>0.02010526075751034</v>
       </c>
       <c r="C7" s="2">
-        <v>113.1127432298365</v>
+        <v>113.1127432298366</v>
       </c>
       <c r="D7" s="2">
         <v>0.02010526075751034</v>
@@ -532,10 +532,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>0.02115472587474057</v>
+        <v>0.02115472587474058</v>
       </c>
       <c r="C8" s="2">
-        <v>111.890141644752</v>
+        <v>111.8901416447521</v>
       </c>
       <c r="D8" s="2">
         <v>0.02115472587474057</v>
@@ -563,10 +563,10 @@
         <v>0.009874442569049225</v>
       </c>
       <c r="C10" s="2">
-        <v>121.7676313670849</v>
+        <v>121.767631367085</v>
       </c>
       <c r="D10" s="2">
-        <v>0.009874442569049225</v>
+        <v>0.009874442569049223</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -577,10 +577,10 @@
         <v>0.0511185110208276</v>
       </c>
       <c r="C11" s="2">
-        <v>128.7319396570368</v>
+        <v>128.7319396570367</v>
       </c>
       <c r="D11" s="2">
-        <v>0.0511185110208276</v>
+        <v>0.05111851102082758</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -588,10 +588,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1573709494792595</v>
+        <v>0.1573709494792596</v>
       </c>
       <c r="C12" s="2">
-        <v>116.2077557214536</v>
+        <v>116.2077557214537</v>
       </c>
       <c r="D12" s="2">
         <v>0.1573709494792595</v>
@@ -605,7 +605,7 @@
         <v>0.02822217101723061</v>
       </c>
       <c r="C13" s="2">
-        <v>101.6164792396495</v>
+        <v>101.6164792396494</v>
       </c>
       <c r="D13" s="2">
         <v>0.02822217101723061</v>
@@ -619,10 +619,10 @@
         <v>0.005563922185213122</v>
       </c>
       <c r="C14" s="2">
-        <v>128.7324815389222</v>
+        <v>128.7324815389223</v>
       </c>
       <c r="D14" s="2">
-        <v>0.005563922185213122</v>
+        <v>0.005563922185213121</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -630,13 +630,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2">
-        <v>0.02337999567124581</v>
+        <v>0.0233799956712458</v>
       </c>
       <c r="C15" s="2">
-        <v>101.699913487983</v>
+        <v>101.6999134879831</v>
       </c>
       <c r="D15" s="2">
-        <v>0.02337999567124581</v>
+        <v>0.0233799956712458</v>
       </c>
     </row>
   </sheetData>
